--- a/Vulnerability Test Results/Appium_E2E_Test_Report_Final.xlsx
+++ b/Vulnerability Test Results/Appium_E2E_Test_Report_Final.xlsx
@@ -53,7 +53,7 @@
     <t>Average Execution Time (sec)</t>
   </si>
   <si>
-    <t>1.84</t>
+    <t>1.78</t>
   </si>
   <si>
     <t>Overall Health Rating</t>
@@ -3164,7 +3164,7 @@
         <v>30</v>
       </c>
       <c r="G2" s="7">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>31</v>
@@ -3193,7 +3193,7 @@
         <v>30</v>
       </c>
       <c r="G3" s="7">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>31</v>
@@ -3222,7 +3222,7 @@
         <v>30</v>
       </c>
       <c r="G4" s="7">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>31</v>
@@ -3251,7 +3251,7 @@
         <v>30</v>
       </c>
       <c r="G5" s="7">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>31</v>
@@ -3280,7 +3280,7 @@
         <v>30</v>
       </c>
       <c r="G6" s="7">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>31</v>
@@ -3309,7 +3309,7 @@
         <v>30</v>
       </c>
       <c r="G7" s="7">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>31</v>
@@ -3338,7 +3338,7 @@
         <v>30</v>
       </c>
       <c r="G8" s="7">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>31</v>
@@ -3367,7 +3367,7 @@
         <v>30</v>
       </c>
       <c r="G9" s="7">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>31</v>
@@ -3396,7 +3396,7 @@
         <v>30</v>
       </c>
       <c r="G10" s="7">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>31</v>
@@ -3454,7 +3454,7 @@
         <v>30</v>
       </c>
       <c r="G12" s="7">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>31</v>
@@ -3483,7 +3483,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="7">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>31</v>
@@ -3512,7 +3512,7 @@
         <v>30</v>
       </c>
       <c r="G14" s="7">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>31</v>
@@ -3541,7 +3541,7 @@
         <v>30</v>
       </c>
       <c r="G15" s="7">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>31</v>
@@ -3570,7 +3570,7 @@
         <v>30</v>
       </c>
       <c r="G16" s="7">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>31</v>
@@ -3599,7 +3599,7 @@
         <v>30</v>
       </c>
       <c r="G17" s="7">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>31</v>
@@ -3628,7 +3628,7 @@
         <v>30</v>
       </c>
       <c r="G18" s="7">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="H18" s="8" t="s">
         <v>31</v>
@@ -3657,7 +3657,7 @@
         <v>30</v>
       </c>
       <c r="G19" s="7">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>31</v>
@@ -3686,7 +3686,7 @@
         <v>30</v>
       </c>
       <c r="G20" s="7">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>31</v>
@@ -3715,7 +3715,7 @@
         <v>30</v>
       </c>
       <c r="G21" s="7">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>31</v>
@@ -3744,7 +3744,7 @@
         <v>30</v>
       </c>
       <c r="G22" s="7">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>31</v>
@@ -3773,7 +3773,7 @@
         <v>30</v>
       </c>
       <c r="G23" s="7">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>31</v>
@@ -3802,7 +3802,7 @@
         <v>30</v>
       </c>
       <c r="G24" s="7">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>31</v>
@@ -3831,7 +3831,7 @@
         <v>30</v>
       </c>
       <c r="G25" s="7">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>31</v>
@@ -3860,7 +3860,7 @@
         <v>30</v>
       </c>
       <c r="G26" s="7">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>31</v>
@@ -3889,7 +3889,7 @@
         <v>30</v>
       </c>
       <c r="G27" s="7">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>31</v>
@@ -3918,7 +3918,7 @@
         <v>30</v>
       </c>
       <c r="G28" s="7">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>31</v>
@@ -3947,7 +3947,7 @@
         <v>30</v>
       </c>
       <c r="G29" s="7">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>31</v>
@@ -3976,7 +3976,7 @@
         <v>30</v>
       </c>
       <c r="G30" s="7">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>31</v>
@@ -4005,7 +4005,7 @@
         <v>30</v>
       </c>
       <c r="G31" s="7">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>31</v>
@@ -4034,7 +4034,7 @@
         <v>30</v>
       </c>
       <c r="G32" s="7">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>31</v>
@@ -4063,7 +4063,7 @@
         <v>30</v>
       </c>
       <c r="G33" s="7">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>31</v>
@@ -4092,7 +4092,7 @@
         <v>30</v>
       </c>
       <c r="G34" s="7">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>31</v>
@@ -4121,7 +4121,7 @@
         <v>30</v>
       </c>
       <c r="G35" s="7">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>31</v>
@@ -4179,7 +4179,7 @@
         <v>30</v>
       </c>
       <c r="G37" s="7">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="H37" s="8" t="s">
         <v>31</v>
@@ -4208,7 +4208,7 @@
         <v>30</v>
       </c>
       <c r="G38" s="7">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>31</v>
@@ -4237,7 +4237,7 @@
         <v>30</v>
       </c>
       <c r="G39" s="7">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="H39" s="8" t="s">
         <v>31</v>
@@ -4266,7 +4266,7 @@
         <v>30</v>
       </c>
       <c r="G40" s="7">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>31</v>
@@ -4295,7 +4295,7 @@
         <v>30</v>
       </c>
       <c r="G41" s="7">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="H41" s="8" t="s">
         <v>31</v>
@@ -4324,7 +4324,7 @@
         <v>30</v>
       </c>
       <c r="G42" s="7">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="H42" s="8" t="s">
         <v>31</v>
@@ -4353,7 +4353,7 @@
         <v>30</v>
       </c>
       <c r="G43" s="7">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H43" s="8" t="s">
         <v>31</v>
@@ -4382,7 +4382,7 @@
         <v>30</v>
       </c>
       <c r="G44" s="7">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="H44" s="8" t="s">
         <v>31</v>
@@ -4411,7 +4411,7 @@
         <v>30</v>
       </c>
       <c r="G45" s="7">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="H45" s="8" t="s">
         <v>31</v>
@@ -4440,7 +4440,7 @@
         <v>30</v>
       </c>
       <c r="G46" s="7">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="H46" s="8" t="s">
         <v>31</v>
@@ -4469,7 +4469,7 @@
         <v>30</v>
       </c>
       <c r="G47" s="7">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="H47" s="8" t="s">
         <v>31</v>
@@ -4498,7 +4498,7 @@
         <v>30</v>
       </c>
       <c r="G48" s="7">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="H48" s="8" t="s">
         <v>31</v>
@@ -4527,7 +4527,7 @@
         <v>30</v>
       </c>
       <c r="G49" s="7">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="H49" s="8" t="s">
         <v>31</v>
@@ -4556,7 +4556,7 @@
         <v>30</v>
       </c>
       <c r="G50" s="7">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>31</v>
@@ -4585,7 +4585,7 @@
         <v>30</v>
       </c>
       <c r="G51" s="7">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H51" s="8" t="s">
         <v>31</v>
@@ -4614,7 +4614,7 @@
         <v>30</v>
       </c>
       <c r="G52" s="7">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="H52" s="8" t="s">
         <v>31</v>
@@ -4643,7 +4643,7 @@
         <v>30</v>
       </c>
       <c r="G53" s="7">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="H53" s="8" t="s">
         <v>31</v>
@@ -4672,7 +4672,7 @@
         <v>30</v>
       </c>
       <c r="G54" s="7">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="H54" s="8" t="s">
         <v>31</v>
@@ -4701,7 +4701,7 @@
         <v>30</v>
       </c>
       <c r="G55" s="7">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="H55" s="8" t="s">
         <v>31</v>
@@ -4730,7 +4730,7 @@
         <v>30</v>
       </c>
       <c r="G56" s="7">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H56" s="8" t="s">
         <v>31</v>
@@ -4788,7 +4788,7 @@
         <v>30</v>
       </c>
       <c r="G58" s="7">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="H58" s="8" t="s">
         <v>31</v>
@@ -4817,7 +4817,7 @@
         <v>30</v>
       </c>
       <c r="G59" s="7">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="H59" s="8" t="s">
         <v>31</v>
@@ -4846,7 +4846,7 @@
         <v>30</v>
       </c>
       <c r="G60" s="7">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H60" s="8" t="s">
         <v>31</v>
@@ -4875,7 +4875,7 @@
         <v>30</v>
       </c>
       <c r="G61" s="7">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="H61" s="8" t="s">
         <v>31</v>
@@ -4904,7 +4904,7 @@
         <v>30</v>
       </c>
       <c r="G62" s="7">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="H62" s="8" t="s">
         <v>31</v>
@@ -4933,7 +4933,7 @@
         <v>30</v>
       </c>
       <c r="G63" s="7">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="H63" s="8" t="s">
         <v>31</v>
@@ -4962,7 +4962,7 @@
         <v>30</v>
       </c>
       <c r="G64" s="7">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="H64" s="8" t="s">
         <v>31</v>
@@ -4991,7 +4991,7 @@
         <v>30</v>
       </c>
       <c r="G65" s="7">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="H65" s="8" t="s">
         <v>31</v>
@@ -5049,7 +5049,7 @@
         <v>30</v>
       </c>
       <c r="G67" s="7">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="H67" s="8" t="s">
         <v>31</v>
@@ -5078,7 +5078,7 @@
         <v>30</v>
       </c>
       <c r="G68" s="7">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="H68" s="8" t="s">
         <v>31</v>
@@ -5107,7 +5107,7 @@
         <v>30</v>
       </c>
       <c r="G69" s="7">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="H69" s="8" t="s">
         <v>31</v>
@@ -5136,7 +5136,7 @@
         <v>30</v>
       </c>
       <c r="G70" s="7">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="H70" s="8" t="s">
         <v>31</v>
@@ -5165,7 +5165,7 @@
         <v>30</v>
       </c>
       <c r="G71" s="7">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="H71" s="8" t="s">
         <v>31</v>
@@ -5194,7 +5194,7 @@
         <v>30</v>
       </c>
       <c r="G72" s="7">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="H72" s="8" t="s">
         <v>31</v>
@@ -5223,7 +5223,7 @@
         <v>30</v>
       </c>
       <c r="G73" s="7">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="H73" s="8" t="s">
         <v>31</v>
@@ -5252,7 +5252,7 @@
         <v>30</v>
       </c>
       <c r="G74" s="7">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="H74" s="8" t="s">
         <v>31</v>
@@ -5281,7 +5281,7 @@
         <v>30</v>
       </c>
       <c r="G75" s="7">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H75" s="8" t="s">
         <v>31</v>
@@ -5310,7 +5310,7 @@
         <v>30</v>
       </c>
       <c r="G76" s="7">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="H76" s="8" t="s">
         <v>31</v>
@@ -5339,7 +5339,7 @@
         <v>30</v>
       </c>
       <c r="G77" s="7">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="H77" s="8" t="s">
         <v>31</v>
@@ -5368,7 +5368,7 @@
         <v>30</v>
       </c>
       <c r="G78" s="7">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="H78" s="8" t="s">
         <v>31</v>
@@ -5397,7 +5397,7 @@
         <v>30</v>
       </c>
       <c r="G79" s="7">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="H79" s="8" t="s">
         <v>31</v>
@@ -5426,7 +5426,7 @@
         <v>30</v>
       </c>
       <c r="G80" s="7">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="H80" s="8" t="s">
         <v>31</v>
@@ -5455,7 +5455,7 @@
         <v>30</v>
       </c>
       <c r="G81" s="7">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="H81" s="8" t="s">
         <v>31</v>
@@ -5484,7 +5484,7 @@
         <v>30</v>
       </c>
       <c r="G82" s="7">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="H82" s="8" t="s">
         <v>31</v>
@@ -5513,7 +5513,7 @@
         <v>30</v>
       </c>
       <c r="G83" s="7">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="H83" s="8" t="s">
         <v>31</v>
@@ -5542,7 +5542,7 @@
         <v>30</v>
       </c>
       <c r="G84" s="7">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="H84" s="8" t="s">
         <v>31</v>
@@ -5571,7 +5571,7 @@
         <v>30</v>
       </c>
       <c r="G85" s="7">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="H85" s="8" t="s">
         <v>31</v>
@@ -5600,7 +5600,7 @@
         <v>30</v>
       </c>
       <c r="G86" s="7">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H86" s="8" t="s">
         <v>31</v>
@@ -5629,7 +5629,7 @@
         <v>30</v>
       </c>
       <c r="G87" s="7">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="H87" s="8" t="s">
         <v>31</v>
@@ -5658,7 +5658,7 @@
         <v>30</v>
       </c>
       <c r="G88" s="7">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="H88" s="8" t="s">
         <v>31</v>
@@ -5687,7 +5687,7 @@
         <v>30</v>
       </c>
       <c r="G89" s="7">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="H89" s="8" t="s">
         <v>31</v>
@@ -5716,7 +5716,7 @@
         <v>30</v>
       </c>
       <c r="G90" s="7">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="H90" s="8" t="s">
         <v>31</v>
@@ -5745,7 +5745,7 @@
         <v>30</v>
       </c>
       <c r="G91" s="7">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H91" s="8" t="s">
         <v>31</v>
@@ -5774,7 +5774,7 @@
         <v>30</v>
       </c>
       <c r="G92" s="7">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="H92" s="8" t="s">
         <v>31</v>
@@ -5803,7 +5803,7 @@
         <v>30</v>
       </c>
       <c r="G93" s="7">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="H93" s="8" t="s">
         <v>31</v>
@@ -5832,7 +5832,7 @@
         <v>30</v>
       </c>
       <c r="G94" s="7">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="H94" s="8" t="s">
         <v>31</v>
@@ -5861,7 +5861,7 @@
         <v>30</v>
       </c>
       <c r="G95" s="7">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="H95" s="8" t="s">
         <v>31</v>
@@ -5890,7 +5890,7 @@
         <v>30</v>
       </c>
       <c r="G96" s="7">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="H96" s="8" t="s">
         <v>31</v>
@@ -5919,7 +5919,7 @@
         <v>30</v>
       </c>
       <c r="G97" s="7">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="H97" s="8" t="s">
         <v>31</v>
@@ -5948,7 +5948,7 @@
         <v>30</v>
       </c>
       <c r="G98" s="7">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="H98" s="8" t="s">
         <v>31</v>
@@ -5977,7 +5977,7 @@
         <v>30</v>
       </c>
       <c r="G99" s="7">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="H99" s="8" t="s">
         <v>31</v>
@@ -6006,7 +6006,7 @@
         <v>30</v>
       </c>
       <c r="G100" s="7">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="H100" s="8" t="s">
         <v>31</v>
@@ -6035,7 +6035,7 @@
         <v>30</v>
       </c>
       <c r="G101" s="7">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="H101" s="8" t="s">
         <v>31</v>
@@ -6064,7 +6064,7 @@
         <v>30</v>
       </c>
       <c r="G102" s="7">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="H102" s="8" t="s">
         <v>31</v>
@@ -6093,7 +6093,7 @@
         <v>30</v>
       </c>
       <c r="G103" s="7">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="H103" s="8" t="s">
         <v>31</v>
@@ -6122,7 +6122,7 @@
         <v>30</v>
       </c>
       <c r="G104" s="7">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="H104" s="8" t="s">
         <v>31</v>
@@ -6151,7 +6151,7 @@
         <v>30</v>
       </c>
       <c r="G105" s="7">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="H105" s="8" t="s">
         <v>31</v>
@@ -6180,7 +6180,7 @@
         <v>30</v>
       </c>
       <c r="G106" s="7">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="H106" s="8" t="s">
         <v>31</v>
@@ -6209,7 +6209,7 @@
         <v>30</v>
       </c>
       <c r="G107" s="7">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="H107" s="8" t="s">
         <v>31</v>
@@ -6238,7 +6238,7 @@
         <v>30</v>
       </c>
       <c r="G108" s="7">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="H108" s="8" t="s">
         <v>31</v>
@@ -6267,7 +6267,7 @@
         <v>30</v>
       </c>
       <c r="G109" s="7">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="H109" s="8" t="s">
         <v>31</v>
@@ -6296,7 +6296,7 @@
         <v>30</v>
       </c>
       <c r="G110" s="7">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="H110" s="8" t="s">
         <v>31</v>
@@ -6325,7 +6325,7 @@
         <v>30</v>
       </c>
       <c r="G111" s="7">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="H111" s="8" t="s">
         <v>31</v>
@@ -6354,7 +6354,7 @@
         <v>30</v>
       </c>
       <c r="G112" s="7">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="H112" s="8" t="s">
         <v>31</v>
@@ -6383,7 +6383,7 @@
         <v>30</v>
       </c>
       <c r="G113" s="7">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="H113" s="8" t="s">
         <v>31</v>
@@ -6412,7 +6412,7 @@
         <v>30</v>
       </c>
       <c r="G114" s="7">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H114" s="8" t="s">
         <v>31</v>
@@ -6441,7 +6441,7 @@
         <v>30</v>
       </c>
       <c r="G115" s="7">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="H115" s="8" t="s">
         <v>31</v>
@@ -6499,7 +6499,7 @@
         <v>30</v>
       </c>
       <c r="G117" s="7">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="H117" s="8" t="s">
         <v>31</v>
@@ -6528,7 +6528,7 @@
         <v>30</v>
       </c>
       <c r="G118" s="7">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="H118" s="8" t="s">
         <v>31</v>
@@ -6557,7 +6557,7 @@
         <v>30</v>
       </c>
       <c r="G119" s="7">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="H119" s="8" t="s">
         <v>31</v>
@@ -6586,7 +6586,7 @@
         <v>30</v>
       </c>
       <c r="G120" s="7">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="H120" s="8" t="s">
         <v>31</v>
@@ -6615,7 +6615,7 @@
         <v>30</v>
       </c>
       <c r="G121" s="7">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="H121" s="8" t="s">
         <v>31</v>
@@ -6644,7 +6644,7 @@
         <v>30</v>
       </c>
       <c r="G122" s="7">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="H122" s="8" t="s">
         <v>31</v>
@@ -6673,7 +6673,7 @@
         <v>30</v>
       </c>
       <c r="G123" s="7">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H123" s="8" t="s">
         <v>31</v>
@@ -6702,7 +6702,7 @@
         <v>30</v>
       </c>
       <c r="G124" s="7">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="H124" s="8" t="s">
         <v>31</v>
@@ -6731,7 +6731,7 @@
         <v>30</v>
       </c>
       <c r="G125" s="7">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H125" s="8" t="s">
         <v>31</v>
@@ -6760,7 +6760,7 @@
         <v>30</v>
       </c>
       <c r="G126" s="7">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="H126" s="8" t="s">
         <v>31</v>
@@ -6789,7 +6789,7 @@
         <v>30</v>
       </c>
       <c r="G127" s="7">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="H127" s="8" t="s">
         <v>31</v>
@@ -6818,7 +6818,7 @@
         <v>30</v>
       </c>
       <c r="G128" s="7">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="H128" s="8" t="s">
         <v>31</v>
@@ -6847,7 +6847,7 @@
         <v>30</v>
       </c>
       <c r="G129" s="7">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="H129" s="8" t="s">
         <v>31</v>
@@ -6876,7 +6876,7 @@
         <v>30</v>
       </c>
       <c r="G130" s="7">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="H130" s="8" t="s">
         <v>31</v>
@@ -6905,7 +6905,7 @@
         <v>30</v>
       </c>
       <c r="G131" s="7">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="H131" s="8" t="s">
         <v>31</v>
@@ -6934,7 +6934,7 @@
         <v>30</v>
       </c>
       <c r="G132" s="7">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="H132" s="8" t="s">
         <v>31</v>
@@ -6963,7 +6963,7 @@
         <v>30</v>
       </c>
       <c r="G133" s="7">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="H133" s="8" t="s">
         <v>31</v>
@@ -6992,7 +6992,7 @@
         <v>30</v>
       </c>
       <c r="G134" s="7">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H134" s="8" t="s">
         <v>31</v>
@@ -7021,7 +7021,7 @@
         <v>30</v>
       </c>
       <c r="G135" s="7">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="H135" s="8" t="s">
         <v>31</v>
@@ -7050,7 +7050,7 @@
         <v>30</v>
       </c>
       <c r="G136" s="7">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="H136" s="8" t="s">
         <v>31</v>
@@ -7079,7 +7079,7 @@
         <v>30</v>
       </c>
       <c r="G137" s="7">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="H137" s="8" t="s">
         <v>31</v>
@@ -7108,7 +7108,7 @@
         <v>30</v>
       </c>
       <c r="G138" s="7">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H138" s="8" t="s">
         <v>31</v>
@@ -7137,7 +7137,7 @@
         <v>30</v>
       </c>
       <c r="G139" s="7">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="H139" s="8" t="s">
         <v>31</v>
@@ -7166,7 +7166,7 @@
         <v>30</v>
       </c>
       <c r="G140" s="7">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="H140" s="8" t="s">
         <v>31</v>
@@ -7195,7 +7195,7 @@
         <v>30</v>
       </c>
       <c r="G141" s="7">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="H141" s="8" t="s">
         <v>31</v>
@@ -7224,7 +7224,7 @@
         <v>30</v>
       </c>
       <c r="G142" s="7">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="H142" s="8" t="s">
         <v>31</v>
@@ -7253,7 +7253,7 @@
         <v>30</v>
       </c>
       <c r="G143" s="7">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H143" s="8" t="s">
         <v>31</v>
@@ -7282,7 +7282,7 @@
         <v>30</v>
       </c>
       <c r="G144" s="7">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H144" s="8" t="s">
         <v>31</v>
@@ -7311,7 +7311,7 @@
         <v>30</v>
       </c>
       <c r="G145" s="7">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="H145" s="8" t="s">
         <v>31</v>
@@ -7340,7 +7340,7 @@
         <v>30</v>
       </c>
       <c r="G146" s="7">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H146" s="8" t="s">
         <v>31</v>
@@ -7369,7 +7369,7 @@
         <v>30</v>
       </c>
       <c r="G147" s="7">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="H147" s="8" t="s">
         <v>31</v>
@@ -7398,7 +7398,7 @@
         <v>30</v>
       </c>
       <c r="G148" s="7">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="H148" s="8" t="s">
         <v>31</v>
@@ -7427,7 +7427,7 @@
         <v>30</v>
       </c>
       <c r="G149" s="7">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="H149" s="8" t="s">
         <v>31</v>
@@ -7456,7 +7456,7 @@
         <v>30</v>
       </c>
       <c r="G150" s="7">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="H150" s="8" t="s">
         <v>31</v>
@@ -7485,7 +7485,7 @@
         <v>30</v>
       </c>
       <c r="G151" s="7">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="H151" s="8" t="s">
         <v>31</v>
@@ -7514,7 +7514,7 @@
         <v>30</v>
       </c>
       <c r="G152" s="7">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="H152" s="8" t="s">
         <v>31</v>
@@ -7543,7 +7543,7 @@
         <v>30</v>
       </c>
       <c r="G153" s="7">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="H153" s="8" t="s">
         <v>31</v>
@@ -7572,7 +7572,7 @@
         <v>30</v>
       </c>
       <c r="G154" s="7">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="H154" s="8" t="s">
         <v>31</v>
@@ -7601,7 +7601,7 @@
         <v>30</v>
       </c>
       <c r="G155" s="7">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="H155" s="8" t="s">
         <v>31</v>
@@ -7630,7 +7630,7 @@
         <v>30</v>
       </c>
       <c r="G156" s="7">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="H156" s="8" t="s">
         <v>31</v>
@@ -7659,7 +7659,7 @@
         <v>30</v>
       </c>
       <c r="G157" s="7">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="H157" s="8" t="s">
         <v>31</v>
@@ -7688,7 +7688,7 @@
         <v>30</v>
       </c>
       <c r="G158" s="7">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="H158" s="8" t="s">
         <v>31</v>
@@ -7717,7 +7717,7 @@
         <v>30</v>
       </c>
       <c r="G159" s="7">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="H159" s="8" t="s">
         <v>31</v>
@@ -7746,7 +7746,7 @@
         <v>30</v>
       </c>
       <c r="G160" s="7">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="H160" s="8" t="s">
         <v>31</v>
@@ -7775,7 +7775,7 @@
         <v>30</v>
       </c>
       <c r="G161" s="7">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="H161" s="8" t="s">
         <v>31</v>
@@ -7833,7 +7833,7 @@
         <v>30</v>
       </c>
       <c r="G163" s="7">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H163" s="8" t="s">
         <v>31</v>
@@ -7891,7 +7891,7 @@
         <v>30</v>
       </c>
       <c r="G165" s="7">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="H165" s="8" t="s">
         <v>31</v>
@@ -7920,7 +7920,7 @@
         <v>30</v>
       </c>
       <c r="G166" s="7">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H166" s="8" t="s">
         <v>31</v>
@@ -7949,7 +7949,7 @@
         <v>30</v>
       </c>
       <c r="G167" s="7">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="H167" s="8" t="s">
         <v>31</v>
@@ -7978,7 +7978,7 @@
         <v>30</v>
       </c>
       <c r="G168" s="7">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="H168" s="8" t="s">
         <v>31</v>
@@ -8007,7 +8007,7 @@
         <v>30</v>
       </c>
       <c r="G169" s="7">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H169" s="8" t="s">
         <v>31</v>
@@ -8036,7 +8036,7 @@
         <v>30</v>
       </c>
       <c r="G170" s="7">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="H170" s="8" t="s">
         <v>31</v>
@@ -8065,7 +8065,7 @@
         <v>30</v>
       </c>
       <c r="G171" s="7">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="H171" s="8" t="s">
         <v>31</v>
@@ -8094,7 +8094,7 @@
         <v>30</v>
       </c>
       <c r="G172" s="7">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="H172" s="8" t="s">
         <v>31</v>
@@ -8123,7 +8123,7 @@
         <v>30</v>
       </c>
       <c r="G173" s="7">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="H173" s="8" t="s">
         <v>31</v>
@@ -8152,7 +8152,7 @@
         <v>30</v>
       </c>
       <c r="G174" s="7">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="H174" s="8" t="s">
         <v>31</v>
@@ -8181,7 +8181,7 @@
         <v>30</v>
       </c>
       <c r="G175" s="7">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="H175" s="8" t="s">
         <v>31</v>
@@ -8239,7 +8239,7 @@
         <v>30</v>
       </c>
       <c r="G177" s="7">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="H177" s="8" t="s">
         <v>31</v>
@@ -8268,7 +8268,7 @@
         <v>30</v>
       </c>
       <c r="G178" s="7">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="H178" s="8" t="s">
         <v>31</v>
@@ -8297,7 +8297,7 @@
         <v>30</v>
       </c>
       <c r="G179" s="7">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="H179" s="8" t="s">
         <v>31</v>
@@ -8326,7 +8326,7 @@
         <v>30</v>
       </c>
       <c r="G180" s="7">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="H180" s="8" t="s">
         <v>31</v>
@@ -8355,7 +8355,7 @@
         <v>30</v>
       </c>
       <c r="G181" s="7">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H181" s="8" t="s">
         <v>31</v>
@@ -8384,7 +8384,7 @@
         <v>30</v>
       </c>
       <c r="G182" s="7">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="H182" s="8" t="s">
         <v>31</v>
@@ -8413,7 +8413,7 @@
         <v>30</v>
       </c>
       <c r="G183" s="7">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="H183" s="8" t="s">
         <v>31</v>
@@ -8442,7 +8442,7 @@
         <v>30</v>
       </c>
       <c r="G184" s="7">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="H184" s="8" t="s">
         <v>31</v>
@@ -8471,7 +8471,7 @@
         <v>30</v>
       </c>
       <c r="G185" s="7">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H185" s="8" t="s">
         <v>31</v>
@@ -8500,7 +8500,7 @@
         <v>30</v>
       </c>
       <c r="G186" s="7">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="H186" s="8" t="s">
         <v>31</v>
@@ -8529,7 +8529,7 @@
         <v>30</v>
       </c>
       <c r="G187" s="7">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="H187" s="8" t="s">
         <v>31</v>
@@ -8558,7 +8558,7 @@
         <v>30</v>
       </c>
       <c r="G188" s="7">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="H188" s="8" t="s">
         <v>31</v>
@@ -8587,7 +8587,7 @@
         <v>30</v>
       </c>
       <c r="G189" s="7">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="H189" s="8" t="s">
         <v>31</v>
@@ -8616,7 +8616,7 @@
         <v>30</v>
       </c>
       <c r="G190" s="7">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H190" s="8" t="s">
         <v>31</v>
@@ -8645,7 +8645,7 @@
         <v>30</v>
       </c>
       <c r="G191" s="7">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="H191" s="8" t="s">
         <v>31</v>
@@ -8674,7 +8674,7 @@
         <v>30</v>
       </c>
       <c r="G192" s="7">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="H192" s="8" t="s">
         <v>31</v>
@@ -8703,7 +8703,7 @@
         <v>30</v>
       </c>
       <c r="G193" s="7">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H193" s="8" t="s">
         <v>31</v>
@@ -8732,7 +8732,7 @@
         <v>30</v>
       </c>
       <c r="G194" s="7">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="H194" s="8" t="s">
         <v>31</v>
@@ -8761,7 +8761,7 @@
         <v>30</v>
       </c>
       <c r="G195" s="7">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="H195" s="8" t="s">
         <v>31</v>
@@ -8790,7 +8790,7 @@
         <v>30</v>
       </c>
       <c r="G196" s="7">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="H196" s="8" t="s">
         <v>31</v>
@@ -8819,7 +8819,7 @@
         <v>30</v>
       </c>
       <c r="G197" s="7">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="H197" s="8" t="s">
         <v>31</v>
@@ -8848,7 +8848,7 @@
         <v>30</v>
       </c>
       <c r="G198" s="7">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="H198" s="8" t="s">
         <v>31</v>
@@ -8877,7 +8877,7 @@
         <v>30</v>
       </c>
       <c r="G199" s="7">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="H199" s="8" t="s">
         <v>31</v>
@@ -8906,7 +8906,7 @@
         <v>30</v>
       </c>
       <c r="G200" s="7">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="H200" s="8" t="s">
         <v>31</v>
@@ -8964,7 +8964,7 @@
         <v>30</v>
       </c>
       <c r="G202" s="7">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="H202" s="8" t="s">
         <v>31</v>
@@ -8993,7 +8993,7 @@
         <v>30</v>
       </c>
       <c r="G203" s="7">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="H203" s="8" t="s">
         <v>31</v>
@@ -9022,7 +9022,7 @@
         <v>30</v>
       </c>
       <c r="G204" s="7">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="H204" s="8" t="s">
         <v>31</v>
@@ -9051,7 +9051,7 @@
         <v>30</v>
       </c>
       <c r="G205" s="7">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="H205" s="8" t="s">
         <v>31</v>
@@ -9080,7 +9080,7 @@
         <v>30</v>
       </c>
       <c r="G206" s="7">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="H206" s="8" t="s">
         <v>31</v>
@@ -9109,7 +9109,7 @@
         <v>30</v>
       </c>
       <c r="G207" s="7">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="H207" s="8" t="s">
         <v>31</v>
@@ -9138,7 +9138,7 @@
         <v>30</v>
       </c>
       <c r="G208" s="7">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="H208" s="8" t="s">
         <v>31</v>
@@ -9167,7 +9167,7 @@
         <v>30</v>
       </c>
       <c r="G209" s="7">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="H209" s="8" t="s">
         <v>31</v>
@@ -9196,7 +9196,7 @@
         <v>30</v>
       </c>
       <c r="G210" s="7">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="H210" s="8" t="s">
         <v>31</v>
@@ -9225,7 +9225,7 @@
         <v>30</v>
       </c>
       <c r="G211" s="7">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="H211" s="8" t="s">
         <v>31</v>
@@ -9254,7 +9254,7 @@
         <v>30</v>
       </c>
       <c r="G212" s="7">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="H212" s="8" t="s">
         <v>31</v>
@@ -9283,7 +9283,7 @@
         <v>30</v>
       </c>
       <c r="G213" s="7">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="H213" s="8" t="s">
         <v>31</v>
@@ -9341,7 +9341,7 @@
         <v>30</v>
       </c>
       <c r="G215" s="7">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="H215" s="8" t="s">
         <v>31</v>
@@ -9370,7 +9370,7 @@
         <v>30</v>
       </c>
       <c r="G216" s="7">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="H216" s="8" t="s">
         <v>31</v>
@@ -9399,7 +9399,7 @@
         <v>30</v>
       </c>
       <c r="G217" s="7">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="H217" s="8" t="s">
         <v>31</v>
@@ -9428,7 +9428,7 @@
         <v>30</v>
       </c>
       <c r="G218" s="7">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="H218" s="8" t="s">
         <v>31</v>
@@ -9457,7 +9457,7 @@
         <v>30</v>
       </c>
       <c r="G219" s="7">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H219" s="8" t="s">
         <v>31</v>
@@ -9486,7 +9486,7 @@
         <v>30</v>
       </c>
       <c r="G220" s="7">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="H220" s="8" t="s">
         <v>31</v>
@@ -9515,7 +9515,7 @@
         <v>30</v>
       </c>
       <c r="G221" s="7">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="H221" s="8" t="s">
         <v>31</v>
@@ -9544,7 +9544,7 @@
         <v>30</v>
       </c>
       <c r="G222" s="7">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="H222" s="8" t="s">
         <v>31</v>
@@ -9573,7 +9573,7 @@
         <v>30</v>
       </c>
       <c r="G223" s="7">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H223" s="8" t="s">
         <v>31</v>
@@ -9602,7 +9602,7 @@
         <v>30</v>
       </c>
       <c r="G224" s="7">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H224" s="8" t="s">
         <v>31</v>
@@ -9631,7 +9631,7 @@
         <v>30</v>
       </c>
       <c r="G225" s="7">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H225" s="8" t="s">
         <v>31</v>
@@ -9660,7 +9660,7 @@
         <v>30</v>
       </c>
       <c r="G226" s="7">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="H226" s="8" t="s">
         <v>31</v>
@@ -9689,7 +9689,7 @@
         <v>30</v>
       </c>
       <c r="G227" s="7">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="H227" s="8" t="s">
         <v>31</v>
@@ -9718,7 +9718,7 @@
         <v>30</v>
       </c>
       <c r="G228" s="7">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="H228" s="8" t="s">
         <v>31</v>
@@ -9747,7 +9747,7 @@
         <v>30</v>
       </c>
       <c r="G229" s="7">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="H229" s="8" t="s">
         <v>31</v>
@@ -9776,7 +9776,7 @@
         <v>30</v>
       </c>
       <c r="G230" s="7">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H230" s="8" t="s">
         <v>31</v>
@@ -9805,7 +9805,7 @@
         <v>30</v>
       </c>
       <c r="G231" s="7">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H231" s="8" t="s">
         <v>31</v>
@@ -9834,7 +9834,7 @@
         <v>30</v>
       </c>
       <c r="G232" s="7">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="H232" s="8" t="s">
         <v>31</v>
@@ -9863,7 +9863,7 @@
         <v>30</v>
       </c>
       <c r="G233" s="7">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="H233" s="8" t="s">
         <v>31</v>
@@ -9892,7 +9892,7 @@
         <v>30</v>
       </c>
       <c r="G234" s="7">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H234" s="8" t="s">
         <v>31</v>
@@ -9921,7 +9921,7 @@
         <v>30</v>
       </c>
       <c r="G235" s="7">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="H235" s="8" t="s">
         <v>31</v>
@@ -9950,7 +9950,7 @@
         <v>30</v>
       </c>
       <c r="G236" s="7">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="H236" s="8" t="s">
         <v>31</v>
@@ -9979,7 +9979,7 @@
         <v>30</v>
       </c>
       <c r="G237" s="7">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="H237" s="8" t="s">
         <v>31</v>
@@ -10008,7 +10008,7 @@
         <v>30</v>
       </c>
       <c r="G238" s="7">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="H238" s="8" t="s">
         <v>31</v>
@@ -10037,7 +10037,7 @@
         <v>30</v>
       </c>
       <c r="G239" s="7">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="H239" s="8" t="s">
         <v>31</v>
@@ -10066,7 +10066,7 @@
         <v>30</v>
       </c>
       <c r="G240" s="7">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="H240" s="8" t="s">
         <v>31</v>
@@ -10095,7 +10095,7 @@
         <v>30</v>
       </c>
       <c r="G241" s="7">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="H241" s="8" t="s">
         <v>31</v>
@@ -10124,7 +10124,7 @@
         <v>30</v>
       </c>
       <c r="G242" s="7">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="H242" s="8" t="s">
         <v>31</v>
@@ -10153,7 +10153,7 @@
         <v>30</v>
       </c>
       <c r="G243" s="7">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="H243" s="8" t="s">
         <v>31</v>
@@ -10182,7 +10182,7 @@
         <v>30</v>
       </c>
       <c r="G244" s="7">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="H244" s="8" t="s">
         <v>31</v>
@@ -10211,7 +10211,7 @@
         <v>30</v>
       </c>
       <c r="G245" s="7">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="H245" s="8" t="s">
         <v>31</v>
@@ -10240,7 +10240,7 @@
         <v>30</v>
       </c>
       <c r="G246" s="7">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="H246" s="8" t="s">
         <v>31</v>
@@ -10269,7 +10269,7 @@
         <v>30</v>
       </c>
       <c r="G247" s="7">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="H247" s="8" t="s">
         <v>31</v>
@@ -10298,7 +10298,7 @@
         <v>30</v>
       </c>
       <c r="G248" s="7">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="H248" s="8" t="s">
         <v>31</v>
@@ -10327,7 +10327,7 @@
         <v>30</v>
       </c>
       <c r="G249" s="7">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="H249" s="8" t="s">
         <v>31</v>
@@ -10356,7 +10356,7 @@
         <v>30</v>
       </c>
       <c r="G250" s="7">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="H250" s="8" t="s">
         <v>31</v>
@@ -10385,7 +10385,7 @@
         <v>30</v>
       </c>
       <c r="G251" s="7">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H251" s="8" t="s">
         <v>31</v>
@@ -10414,7 +10414,7 @@
         <v>30</v>
       </c>
       <c r="G252" s="7">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H252" s="8" t="s">
         <v>31</v>
@@ -10443,7 +10443,7 @@
         <v>30</v>
       </c>
       <c r="G253" s="7">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="H253" s="8" t="s">
         <v>31</v>
@@ -10501,7 +10501,7 @@
         <v>30</v>
       </c>
       <c r="G255" s="7">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="H255" s="8" t="s">
         <v>31</v>
@@ -10530,7 +10530,7 @@
         <v>30</v>
       </c>
       <c r="G256" s="7">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="H256" s="8" t="s">
         <v>31</v>
@@ -10559,7 +10559,7 @@
         <v>30</v>
       </c>
       <c r="G257" s="7">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="H257" s="8" t="s">
         <v>31</v>
@@ -10588,7 +10588,7 @@
         <v>30</v>
       </c>
       <c r="G258" s="7">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="H258" s="8" t="s">
         <v>31</v>
@@ -10617,7 +10617,7 @@
         <v>30</v>
       </c>
       <c r="G259" s="7">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="H259" s="8" t="s">
         <v>31</v>
@@ -10646,7 +10646,7 @@
         <v>30</v>
       </c>
       <c r="G260" s="7">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="H260" s="8" t="s">
         <v>31</v>
@@ -10675,7 +10675,7 @@
         <v>30</v>
       </c>
       <c r="G261" s="7">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="H261" s="8" t="s">
         <v>31</v>
@@ -10704,7 +10704,7 @@
         <v>30</v>
       </c>
       <c r="G262" s="7">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="H262" s="8" t="s">
         <v>31</v>
@@ -10733,7 +10733,7 @@
         <v>30</v>
       </c>
       <c r="G263" s="7">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="H263" s="8" t="s">
         <v>31</v>
@@ -10762,7 +10762,7 @@
         <v>30</v>
       </c>
       <c r="G264" s="7">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="H264" s="8" t="s">
         <v>31</v>
@@ -10820,7 +10820,7 @@
         <v>30</v>
       </c>
       <c r="G266" s="7">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="H266" s="8" t="s">
         <v>31</v>
@@ -10849,7 +10849,7 @@
         <v>30</v>
       </c>
       <c r="G267" s="7">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="H267" s="8" t="s">
         <v>31</v>
@@ -10878,7 +10878,7 @@
         <v>30</v>
       </c>
       <c r="G268" s="7">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="H268" s="8" t="s">
         <v>31</v>
@@ -10907,7 +10907,7 @@
         <v>30</v>
       </c>
       <c r="G269" s="7">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="H269" s="8" t="s">
         <v>31</v>
@@ -10936,7 +10936,7 @@
         <v>30</v>
       </c>
       <c r="G270" s="7">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="H270" s="8" t="s">
         <v>31</v>
@@ -10965,7 +10965,7 @@
         <v>30</v>
       </c>
       <c r="G271" s="7">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="H271" s="8" t="s">
         <v>31</v>
@@ -10994,7 +10994,7 @@
         <v>30</v>
       </c>
       <c r="G272" s="7">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="H272" s="8" t="s">
         <v>31</v>
@@ -11023,7 +11023,7 @@
         <v>30</v>
       </c>
       <c r="G273" s="7">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H273" s="8" t="s">
         <v>31</v>
@@ -11052,7 +11052,7 @@
         <v>30</v>
       </c>
       <c r="G274" s="7">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="H274" s="8" t="s">
         <v>31</v>
@@ -11081,7 +11081,7 @@
         <v>30</v>
       </c>
       <c r="G275" s="7">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="H275" s="8" t="s">
         <v>31</v>
@@ -11110,7 +11110,7 @@
         <v>30</v>
       </c>
       <c r="G276" s="7">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="H276" s="8" t="s">
         <v>31</v>
@@ -11139,7 +11139,7 @@
         <v>30</v>
       </c>
       <c r="G277" s="7">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="H277" s="8" t="s">
         <v>31</v>
@@ -11168,7 +11168,7 @@
         <v>30</v>
       </c>
       <c r="G278" s="7">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H278" s="8" t="s">
         <v>31</v>
@@ -11197,7 +11197,7 @@
         <v>30</v>
       </c>
       <c r="G279" s="7">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="H279" s="8" t="s">
         <v>31</v>
@@ -11226,7 +11226,7 @@
         <v>30</v>
       </c>
       <c r="G280" s="7">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="H280" s="8" t="s">
         <v>31</v>
@@ -11255,7 +11255,7 @@
         <v>30</v>
       </c>
       <c r="G281" s="7">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="H281" s="8" t="s">
         <v>31</v>
@@ -11284,7 +11284,7 @@
         <v>30</v>
       </c>
       <c r="G282" s="7">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="H282" s="8" t="s">
         <v>31</v>
@@ -11313,7 +11313,7 @@
         <v>30</v>
       </c>
       <c r="G283" s="7">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H283" s="8" t="s">
         <v>31</v>
@@ -11342,7 +11342,7 @@
         <v>30</v>
       </c>
       <c r="G284" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H284" s="8" t="s">
         <v>31</v>
@@ -11371,7 +11371,7 @@
         <v>30</v>
       </c>
       <c r="G285" s="7">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H285" s="8" t="s">
         <v>31</v>
@@ -11400,7 +11400,7 @@
         <v>30</v>
       </c>
       <c r="G286" s="7">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="H286" s="8" t="s">
         <v>31</v>
@@ -11429,7 +11429,7 @@
         <v>30</v>
       </c>
       <c r="G287" s="7">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="H287" s="8" t="s">
         <v>31</v>
@@ -11458,7 +11458,7 @@
         <v>30</v>
       </c>
       <c r="G288" s="7">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="H288" s="8" t="s">
         <v>31</v>
@@ -11487,7 +11487,7 @@
         <v>30</v>
       </c>
       <c r="G289" s="7">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="H289" s="8" t="s">
         <v>31</v>
@@ -11516,7 +11516,7 @@
         <v>30</v>
       </c>
       <c r="G290" s="7">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="H290" s="8" t="s">
         <v>31</v>
@@ -11545,7 +11545,7 @@
         <v>30</v>
       </c>
       <c r="G291" s="7">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="H291" s="8" t="s">
         <v>31</v>
@@ -11574,7 +11574,7 @@
         <v>30</v>
       </c>
       <c r="G292" s="7">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="H292" s="8" t="s">
         <v>31</v>
@@ -11603,7 +11603,7 @@
         <v>30</v>
       </c>
       <c r="G293" s="7">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H293" s="8" t="s">
         <v>31</v>
@@ -11632,7 +11632,7 @@
         <v>30</v>
       </c>
       <c r="G294" s="7">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="H294" s="8" t="s">
         <v>31</v>
@@ -11661,7 +11661,7 @@
         <v>30</v>
       </c>
       <c r="G295" s="7">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="H295" s="8" t="s">
         <v>31</v>
@@ -11719,7 +11719,7 @@
         <v>30</v>
       </c>
       <c r="G297" s="7">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="H297" s="8" t="s">
         <v>31</v>
@@ -11748,7 +11748,7 @@
         <v>30</v>
       </c>
       <c r="G298" s="7">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="H298" s="8" t="s">
         <v>31</v>
@@ -11777,7 +11777,7 @@
         <v>30</v>
       </c>
       <c r="G299" s="7">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H299" s="8" t="s">
         <v>31</v>
@@ -11806,7 +11806,7 @@
         <v>30</v>
       </c>
       <c r="G300" s="7">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="H300" s="8" t="s">
         <v>31</v>
@@ -11835,7 +11835,7 @@
         <v>30</v>
       </c>
       <c r="G301" s="7">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="H301" s="8" t="s">
         <v>31</v>
@@ -11864,7 +11864,7 @@
         <v>30</v>
       </c>
       <c r="G302" s="7">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="H302" s="8" t="s">
         <v>31</v>
@@ -11893,7 +11893,7 @@
         <v>30</v>
       </c>
       <c r="G303" s="7">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="H303" s="8" t="s">
         <v>31</v>
@@ -11922,7 +11922,7 @@
         <v>30</v>
       </c>
       <c r="G304" s="7">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="H304" s="8" t="s">
         <v>31</v>
@@ -11980,7 +11980,7 @@
         <v>30</v>
       </c>
       <c r="G306" s="7">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="H306" s="8" t="s">
         <v>31</v>
@@ -12009,7 +12009,7 @@
         <v>30</v>
       </c>
       <c r="G307" s="7">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H307" s="8" t="s">
         <v>31</v>
@@ -12038,7 +12038,7 @@
         <v>30</v>
       </c>
       <c r="G308" s="7">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="H308" s="8" t="s">
         <v>31</v>
@@ -12067,7 +12067,7 @@
         <v>30</v>
       </c>
       <c r="G309" s="7">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="H309" s="8" t="s">
         <v>31</v>
@@ -12096,7 +12096,7 @@
         <v>30</v>
       </c>
       <c r="G310" s="7">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="H310" s="8" t="s">
         <v>31</v>
@@ -12154,7 +12154,7 @@
         <v>30</v>
       </c>
       <c r="G312" s="7">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="H312" s="8" t="s">
         <v>31</v>
@@ -12183,7 +12183,7 @@
         <v>30</v>
       </c>
       <c r="G313" s="7">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="H313" s="8" t="s">
         <v>31</v>
@@ -12212,7 +12212,7 @@
         <v>30</v>
       </c>
       <c r="G314" s="7">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="H314" s="8" t="s">
         <v>31</v>
@@ -12241,7 +12241,7 @@
         <v>30</v>
       </c>
       <c r="G315" s="7">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="H315" s="8" t="s">
         <v>31</v>
@@ -12270,7 +12270,7 @@
         <v>30</v>
       </c>
       <c r="G316" s="7">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="H316" s="8" t="s">
         <v>31</v>
@@ -12299,7 +12299,7 @@
         <v>30</v>
       </c>
       <c r="G317" s="7">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="H317" s="8" t="s">
         <v>31</v>
@@ -12328,7 +12328,7 @@
         <v>30</v>
       </c>
       <c r="G318" s="7">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H318" s="8" t="s">
         <v>31</v>
@@ -12357,7 +12357,7 @@
         <v>30</v>
       </c>
       <c r="G319" s="7">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="H319" s="8" t="s">
         <v>31</v>
@@ -12386,7 +12386,7 @@
         <v>30</v>
       </c>
       <c r="G320" s="7">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H320" s="8" t="s">
         <v>31</v>
@@ -12415,7 +12415,7 @@
         <v>30</v>
       </c>
       <c r="G321" s="7">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="H321" s="8" t="s">
         <v>31</v>
@@ -12444,7 +12444,7 @@
         <v>30</v>
       </c>
       <c r="G322" s="7">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H322" s="8" t="s">
         <v>31</v>
@@ -12473,7 +12473,7 @@
         <v>30</v>
       </c>
       <c r="G323" s="7">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="H323" s="8" t="s">
         <v>31</v>
@@ -12502,7 +12502,7 @@
         <v>30</v>
       </c>
       <c r="G324" s="7">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H324" s="8" t="s">
         <v>31</v>
@@ -12531,7 +12531,7 @@
         <v>30</v>
       </c>
       <c r="G325" s="7">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="H325" s="8" t="s">
         <v>31</v>
@@ -12560,7 +12560,7 @@
         <v>30</v>
       </c>
       <c r="G326" s="7">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="H326" s="8" t="s">
         <v>31</v>
@@ -12589,7 +12589,7 @@
         <v>30</v>
       </c>
       <c r="G327" s="7">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="H327" s="8" t="s">
         <v>31</v>
@@ -12618,7 +12618,7 @@
         <v>30</v>
       </c>
       <c r="G328" s="7">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="H328" s="8" t="s">
         <v>31</v>
@@ -12647,7 +12647,7 @@
         <v>30</v>
       </c>
       <c r="G329" s="7">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="H329" s="8" t="s">
         <v>31</v>
@@ -12676,7 +12676,7 @@
         <v>30</v>
       </c>
       <c r="G330" s="7">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H330" s="8" t="s">
         <v>31</v>
@@ -12705,7 +12705,7 @@
         <v>30</v>
       </c>
       <c r="G331" s="7">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="H331" s="8" t="s">
         <v>31</v>
@@ -12734,7 +12734,7 @@
         <v>30</v>
       </c>
       <c r="G332" s="7">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="H332" s="8" t="s">
         <v>31</v>
@@ -12763,7 +12763,7 @@
         <v>30</v>
       </c>
       <c r="G333" s="7">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="H333" s="8" t="s">
         <v>31</v>
@@ -12792,7 +12792,7 @@
         <v>30</v>
       </c>
       <c r="G334" s="7">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="H334" s="8" t="s">
         <v>31</v>
@@ -12821,7 +12821,7 @@
         <v>30</v>
       </c>
       <c r="G335" s="7">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="H335" s="8" t="s">
         <v>31</v>
@@ -12850,7 +12850,7 @@
         <v>30</v>
       </c>
       <c r="G336" s="7">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="H336" s="8" t="s">
         <v>31</v>
@@ -12879,7 +12879,7 @@
         <v>30</v>
       </c>
       <c r="G337" s="7">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H337" s="8" t="s">
         <v>31</v>
@@ -12908,7 +12908,7 @@
         <v>30</v>
       </c>
       <c r="G338" s="7">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="H338" s="8" t="s">
         <v>31</v>
@@ -12937,7 +12937,7 @@
         <v>30</v>
       </c>
       <c r="G339" s="7">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H339" s="8" t="s">
         <v>31</v>
@@ -12966,7 +12966,7 @@
         <v>30</v>
       </c>
       <c r="G340" s="7">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="H340" s="8" t="s">
         <v>31</v>
@@ -12995,7 +12995,7 @@
         <v>30</v>
       </c>
       <c r="G341" s="7">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="H341" s="8" t="s">
         <v>31</v>
@@ -13024,7 +13024,7 @@
         <v>30</v>
       </c>
       <c r="G342" s="7">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="H342" s="8" t="s">
         <v>31</v>
@@ -13053,7 +13053,7 @@
         <v>30</v>
       </c>
       <c r="G343" s="7">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="H343" s="8" t="s">
         <v>31</v>
@@ -13082,7 +13082,7 @@
         <v>30</v>
       </c>
       <c r="G344" s="7">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="H344" s="8" t="s">
         <v>31</v>
@@ -13111,7 +13111,7 @@
         <v>30</v>
       </c>
       <c r="G345" s="7">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="H345" s="8" t="s">
         <v>31</v>
@@ -13140,7 +13140,7 @@
         <v>30</v>
       </c>
       <c r="G346" s="7">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="H346" s="8" t="s">
         <v>31</v>
@@ -13169,7 +13169,7 @@
         <v>30</v>
       </c>
       <c r="G347" s="7">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="H347" s="8" t="s">
         <v>31</v>
@@ -13198,7 +13198,7 @@
         <v>30</v>
       </c>
       <c r="G348" s="7">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="H348" s="8" t="s">
         <v>31</v>
@@ -13227,7 +13227,7 @@
         <v>30</v>
       </c>
       <c r="G349" s="7">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="H349" s="8" t="s">
         <v>31</v>
@@ -13256,7 +13256,7 @@
         <v>30</v>
       </c>
       <c r="G350" s="7">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="H350" s="8" t="s">
         <v>31</v>
@@ -13285,7 +13285,7 @@
         <v>30</v>
       </c>
       <c r="G351" s="7">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="H351" s="8" t="s">
         <v>31</v>
@@ -13314,7 +13314,7 @@
         <v>30</v>
       </c>
       <c r="G352" s="7">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="H352" s="8" t="s">
         <v>31</v>
@@ -13343,7 +13343,7 @@
         <v>30</v>
       </c>
       <c r="G353" s="7">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="H353" s="8" t="s">
         <v>31</v>
@@ -13372,7 +13372,7 @@
         <v>30</v>
       </c>
       <c r="G354" s="7">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="H354" s="8" t="s">
         <v>31</v>
@@ -13401,7 +13401,7 @@
         <v>30</v>
       </c>
       <c r="G355" s="7">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="H355" s="8" t="s">
         <v>31</v>
@@ -13430,7 +13430,7 @@
         <v>30</v>
       </c>
       <c r="G356" s="7">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="H356" s="8" t="s">
         <v>31</v>
@@ -13459,7 +13459,7 @@
         <v>30</v>
       </c>
       <c r="G357" s="7">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H357" s="8" t="s">
         <v>31</v>
@@ -13488,7 +13488,7 @@
         <v>30</v>
       </c>
       <c r="G358" s="7">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="H358" s="8" t="s">
         <v>31</v>
@@ -13517,7 +13517,7 @@
         <v>30</v>
       </c>
       <c r="G359" s="7">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="H359" s="8" t="s">
         <v>31</v>
@@ -13546,7 +13546,7 @@
         <v>30</v>
       </c>
       <c r="G360" s="7">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H360" s="8" t="s">
         <v>31</v>
@@ -13575,7 +13575,7 @@
         <v>30</v>
       </c>
       <c r="G361" s="7">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="H361" s="8" t="s">
         <v>31</v>
@@ -13604,7 +13604,7 @@
         <v>30</v>
       </c>
       <c r="G362" s="7">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="H362" s="8" t="s">
         <v>31</v>
@@ -13633,7 +13633,7 @@
         <v>30</v>
       </c>
       <c r="G363" s="7">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="H363" s="8" t="s">
         <v>31</v>
@@ -13662,7 +13662,7 @@
         <v>30</v>
       </c>
       <c r="G364" s="7">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="H364" s="8" t="s">
         <v>31</v>
@@ -13691,7 +13691,7 @@
         <v>30</v>
       </c>
       <c r="G365" s="7">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="H365" s="8" t="s">
         <v>31</v>
@@ -13720,7 +13720,7 @@
         <v>30</v>
       </c>
       <c r="G366" s="7">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="H366" s="8" t="s">
         <v>31</v>
@@ -13749,7 +13749,7 @@
         <v>30</v>
       </c>
       <c r="G367" s="7">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="H367" s="8" t="s">
         <v>31</v>
@@ -13778,7 +13778,7 @@
         <v>30</v>
       </c>
       <c r="G368" s="7">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="H368" s="8" t="s">
         <v>31</v>
@@ -13807,7 +13807,7 @@
         <v>30</v>
       </c>
       <c r="G369" s="7">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="H369" s="8" t="s">
         <v>31</v>
@@ -13836,7 +13836,7 @@
         <v>30</v>
       </c>
       <c r="G370" s="7">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H370" s="8" t="s">
         <v>31</v>
@@ -13865,7 +13865,7 @@
         <v>30</v>
       </c>
       <c r="G371" s="7">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="H371" s="8" t="s">
         <v>31</v>
@@ -13894,7 +13894,7 @@
         <v>30</v>
       </c>
       <c r="G372" s="7">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="H372" s="8" t="s">
         <v>31</v>
@@ -13923,7 +13923,7 @@
         <v>30</v>
       </c>
       <c r="G373" s="7">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="H373" s="8" t="s">
         <v>31</v>
@@ -13981,7 +13981,7 @@
         <v>30</v>
       </c>
       <c r="G375" s="7">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="H375" s="8" t="s">
         <v>31</v>
@@ -14010,7 +14010,7 @@
         <v>30</v>
       </c>
       <c r="G376" s="7">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="H376" s="8" t="s">
         <v>31</v>
@@ -14039,7 +14039,7 @@
         <v>30</v>
       </c>
       <c r="G377" s="7">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="H377" s="8" t="s">
         <v>31</v>
@@ -14097,7 +14097,7 @@
         <v>30</v>
       </c>
       <c r="G379" s="7">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="H379" s="8" t="s">
         <v>31</v>
@@ -14126,7 +14126,7 @@
         <v>30</v>
       </c>
       <c r="G380" s="7">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="H380" s="8" t="s">
         <v>31</v>
@@ -14155,7 +14155,7 @@
         <v>30</v>
       </c>
       <c r="G381" s="7">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="H381" s="8" t="s">
         <v>31</v>
@@ -14184,7 +14184,7 @@
         <v>30</v>
       </c>
       <c r="G382" s="7">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="H382" s="8" t="s">
         <v>31</v>
@@ -14213,7 +14213,7 @@
         <v>30</v>
       </c>
       <c r="G383" s="7">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H383" s="8" t="s">
         <v>31</v>
@@ -14242,7 +14242,7 @@
         <v>30</v>
       </c>
       <c r="G384" s="7">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="H384" s="8" t="s">
         <v>31</v>
@@ -14271,7 +14271,7 @@
         <v>30</v>
       </c>
       <c r="G385" s="7">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="H385" s="8" t="s">
         <v>31</v>
@@ -14300,7 +14300,7 @@
         <v>30</v>
       </c>
       <c r="G386" s="7">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="H386" s="8" t="s">
         <v>31</v>
@@ -14329,7 +14329,7 @@
         <v>30</v>
       </c>
       <c r="G387" s="7">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="H387" s="8" t="s">
         <v>31</v>
@@ -14358,7 +14358,7 @@
         <v>30</v>
       </c>
       <c r="G388" s="7">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="H388" s="8" t="s">
         <v>31</v>
@@ -14387,7 +14387,7 @@
         <v>30</v>
       </c>
       <c r="G389" s="7">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="H389" s="8" t="s">
         <v>31</v>
@@ -14416,7 +14416,7 @@
         <v>30</v>
       </c>
       <c r="G390" s="7">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H390" s="8" t="s">
         <v>31</v>
@@ -14445,7 +14445,7 @@
         <v>30</v>
       </c>
       <c r="G391" s="7">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="H391" s="8" t="s">
         <v>31</v>
@@ -14474,7 +14474,7 @@
         <v>30</v>
       </c>
       <c r="G392" s="7">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="H392" s="8" t="s">
         <v>31</v>
@@ -14503,7 +14503,7 @@
         <v>30</v>
       </c>
       <c r="G393" s="7">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="H393" s="8" t="s">
         <v>31</v>
@@ -14532,7 +14532,7 @@
         <v>30</v>
       </c>
       <c r="G394" s="7">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="H394" s="8" t="s">
         <v>31</v>
@@ -14561,7 +14561,7 @@
         <v>30</v>
       </c>
       <c r="G395" s="7">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="H395" s="8" t="s">
         <v>31</v>
@@ -14590,7 +14590,7 @@
         <v>30</v>
       </c>
       <c r="G396" s="7">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="H396" s="8" t="s">
         <v>31</v>
@@ -14619,7 +14619,7 @@
         <v>30</v>
       </c>
       <c r="G397" s="7">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="H397" s="8" t="s">
         <v>31</v>
@@ -14648,7 +14648,7 @@
         <v>30</v>
       </c>
       <c r="G398" s="7">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="H398" s="8" t="s">
         <v>31</v>
@@ -14677,7 +14677,7 @@
         <v>30</v>
       </c>
       <c r="G399" s="7">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="H399" s="8" t="s">
         <v>31</v>
@@ -14706,7 +14706,7 @@
         <v>30</v>
       </c>
       <c r="G400" s="7">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="H400" s="8" t="s">
         <v>31</v>
@@ -14735,7 +14735,7 @@
         <v>30</v>
       </c>
       <c r="G401" s="7">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="H401" s="8" t="s">
         <v>31</v>
